--- a/data/availability/projects/maven-developments/cali-coast-ras-el-hekma.xlsx
+++ b/data/availability/projects/maven-developments/cali-coast-ras-el-hekma.xlsx
@@ -837,7 +837,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1359,7 +1359,6 @@
       <c r="G2" t="n">
         <v>103</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Sea &amp; Lagoons</t>
@@ -1660,7 +1659,6 @@
       <c r="G7" t="n">
         <v>112</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Sea &amp; Lagoons</t>
@@ -1717,7 +1715,6 @@
       <c r="G8" t="n">
         <v>130</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Sea &amp; Lagoons</t>
@@ -1835,7 +1832,6 @@
       <c r="G10" t="n">
         <v>86</v>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>Sea &amp; Lagoons</t>
@@ -1846,7 +1842,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1892,7 +1888,6 @@
       <c r="G11" t="n">
         <v>95</v>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>Sea &amp; Lagoons</t>
@@ -1903,7 +1898,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1964,7 +1959,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -2025,7 +2020,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -2071,7 +2066,6 @@
       <c r="G14" t="n">
         <v>110</v>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>Sea &amp; Lagoons</t>
@@ -2082,7 +2076,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -2128,7 +2122,6 @@
       <c r="G15" t="n">
         <v>150</v>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>Sea &amp; Lagoons</t>
@@ -2139,7 +2132,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2200,7 +2193,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2261,7 +2254,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2322,7 +2315,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2383,7 +2376,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2444,7 +2437,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2505,7 +2498,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2566,7 +2559,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2612,7 +2605,6 @@
       <c r="G23" t="n">
         <v>67</v>
       </c>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>Sea &amp; Lagoons</t>
@@ -2623,7 +2615,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
